--- a/Result/profitability/2722.xlsx
+++ b/Result/profitability/2722.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM69"/>
+  <dimension ref="A1:AM70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-1.42</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.28625</v>
+        <v>-0.3175</v>
       </c>
       <c r="N2" t="n">
-        <v>36.5125</v>
+        <v>34.8475</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>3.09</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08624999999999999</v>
+        <v>0.10375</v>
       </c>
       <c r="N3" t="n">
-        <v>36.04875</v>
+        <v>37.39875000000001</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.71</v>
       </c>
       <c r="M4" t="n">
-        <v>0.21</v>
+        <v>0.21375</v>
       </c>
       <c r="N4" t="n">
-        <v>40.52</v>
+        <v>41.16375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.32</v>
       </c>
       <c r="M5" t="n">
-        <v>0.27125</v>
+        <v>0.26625</v>
       </c>
       <c r="N5" t="n">
-        <v>44.16375</v>
+        <v>43.9675</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.64</v>
       </c>
       <c r="M6" t="n">
-        <v>0.36375</v>
+        <v>0.35375</v>
       </c>
       <c r="N6" t="n">
-        <v>47.1225</v>
+        <v>46.335</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.51</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5599999999999999</v>
+        <v>0.5625</v>
       </c>
       <c r="N7" t="n">
-        <v>50.7875</v>
+        <v>51.3725</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,16 +1391,16 @@
         <v>-0.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0.57875</v>
+        <v>0.5875</v>
       </c>
       <c r="N8" t="n">
-        <v>53.51</v>
+        <v>54.6625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -9207,6 +9207,133 @@
       </c>
       <c r="AM69" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2722</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>147</v>
+      </c>
+      <c r="D70" t="n">
+        <v>100</v>
+      </c>
+      <c r="E70" t="n">
+        <v>47</v>
+      </c>
+      <c r="F70" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-24</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-16.37%</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>-24</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="M70" t="n">
+        <v>-0.12625</v>
+      </c>
+      <c r="N70" t="n">
+        <v>30.7275</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0.06999999999999998</v>
+      </c>
+      <c r="X70" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>9.219999999999999</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>0.4081451969898184</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>-0.04000000000000001</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>0.4000000000000001</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>-1.570000000000004</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>-0.0470341521869384</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK70" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
